--- a/skhynix/dist/20261023_SK海力士模型_v0.4.xlsx
+++ b/skhynix/dist/20261023_SK海力士模型_v0.4.xlsx
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="891">
   <si>
     <r>
       <rPr>
@@ -22211,6 +22211,1570 @@
   </si>
   <si>
     <t xml:space="preserve">2029 EPS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">十年倍數與規則值（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底；見頂年 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位、中段中位數、谷底 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：合理倍數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底倍數依循環位置取分位。多個來源時各自取分位再平均、四捨五入到兩位。倍數歷史為輸入（藍字），來源與標記見各表；原放在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/overview/extract.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">移入）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（主）：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年底</t>
+  </si>
+  <si>
+    <t xml:space="preserve">companiesmarketcap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">marketcapof</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–24</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">標記／說明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">marketcapof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底未提供</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中位數（各來源）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最小（各來源）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大（各來源）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（主）：規則值</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">循環位置</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現價 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：見頂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">見頂年 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中段 → 中位數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：谷底（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">谷底 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底每股淨值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，含虧損年）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">採用（虧損年不計）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">stockanalysis</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（核對，不採用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，含虧損年）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；採用（虧損年不計）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">stockanalysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（核對，不採用）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年虧損（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為負）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">虧損年不計入分位</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2021–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差距 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（對照）：規則值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：見頂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：谷底（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -23994,7 +25558,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
@@ -24002,6 +25566,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="#,##0"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -24112,7 +25677,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -24178,6 +25743,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -24568,12 +26137,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>798</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>799</v>
+        <v>858</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
@@ -24585,7 +26154,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>800</v>
+        <v>859</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -24597,7 +26166,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
@@ -24609,7 +26178,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>802</v>
+        <v>861</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">Mkt!E27</f>
@@ -24621,10 +26190,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>803</v>
+        <v>862</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>804</v>
+        <v>863</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>159</v>
@@ -24655,31 +26224,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>805</v>
+        <v>864</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>806</v>
+        <v>865</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>807</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>808</v>
+        <v>867</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>809</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>810</v>
+        <v>869</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>811</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24687,87 +26256,87 @@
         <v>207</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>812</v>
+        <v>871</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>813</v>
+        <v>872</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>814</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>815</v>
+        <v>874</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>816</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>817</v>
+        <v>876</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>818</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>819</v>
+        <v>878</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>820</v>
+        <v>879</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>821</v>
+        <v>880</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>822</v>
+        <v>881</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>823</v>
+        <v>882</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>824</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>825</v>
+        <v>884</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>826</v>
+        <v>885</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>827</v>
+        <v>886</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>828</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>829</v>
+        <v>888</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>830</v>
+        <v>889</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>831</v>
+        <v>890</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>830</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -33398,10 +34967,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
@@ -34975,6 +36544,802 @@
       <c r="G60" s="11" t="n">
         <f aca="false">F60/px-1</f>
         <v>2.15455001712912</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>0.8832</v>
+      </c>
+      <c r="C70" s="14" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C72" s="14" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C76" s="14" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="B78" s="10" t="n">
+        <f aca="false">PERCENTILE(B68:B77,0.25)</f>
+        <v>1.3175</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <f aca="false">PERCENTILE(C68:C77,0.25)</f>
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="B79" s="10" t="n">
+        <f aca="false">MEDIAN(B68:B77)</f>
+        <v>1.505</v>
+      </c>
+      <c r="C79" s="10" t="n">
+        <f aca="false">MEDIAN(C68:C77)</f>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="B80" s="10" t="n">
+        <f aca="false">PERCENTILE(B68:B77,0.75)</f>
+        <v>1.6125</v>
+      </c>
+      <c r="C80" s="10" t="n">
+        <f aca="false">PERCENTILE(C68:C77,0.75)</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B81" s="10" t="n">
+        <f aca="false">MIN(B68:B77)</f>
+        <v>0.81</v>
+      </c>
+      <c r="C81" s="10" t="n">
+        <f aca="false">MIN(C68:C77)</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B82" s="10" t="n">
+        <f aca="false">MAX(B68:B77)</f>
+        <v>3.86</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <f aca="false">MAX(C68:C77)</f>
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B83" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B78,C78),2)</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="B84" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B79,C79),2)</f>
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="B85" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(B80,C80),2)</f>
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B86" s="10" t="n">
+        <f aca="false">ROUND(MIN(B81,C81),2)</f>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B87" s="10" t="n">
+        <f aca="false">ROUND(MAX(B82,C82),2)</f>
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="C91" s="10" t="n">
+        <f aca="false">B83</f>
+        <v>1.33</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <f aca="false">Y!D28</f>
+        <v>941774.352898496</v>
+      </c>
+      <c r="F91" s="17" t="n">
+        <f aca="false">C91*E91</f>
+        <v>1252559.889355</v>
+      </c>
+      <c r="G91" s="15" t="n">
+        <f aca="false">F91/px-1</f>
+        <v>-0.273035467582705</v>
+      </c>
+      <c r="H91" s="10" t="n">
+        <f aca="false">px/E91</f>
+        <v>1.82952529413986</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <f aca="false">B84</f>
+        <v>1.48</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <f aca="false">Y!D28</f>
+        <v>941774.352898496</v>
+      </c>
+      <c r="F92" s="17" t="n">
+        <f aca="false">C92*E92</f>
+        <v>1393826.04228977</v>
+      </c>
+      <c r="G92" s="15" t="n">
+        <f aca="false">F92/px-1</f>
+        <v>-0.19104698648301</v>
+      </c>
+      <c r="H92" s="10" t="n">
+        <f aca="false">px/E92</f>
+        <v>1.82952529413986</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <f aca="false">B85</f>
+        <v>1.61</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <f aca="false">Y!K28</f>
+        <v>1094692.46613806</v>
+      </c>
+      <c r="F93" s="17" t="n">
+        <f aca="false">C93*E93</f>
+        <v>1762454.87048227</v>
+      </c>
+      <c r="G93" s="15" t="n">
+        <f aca="false">F93/px-1</f>
+        <v>0.0228989381789155</v>
+      </c>
+      <c r="H93" s="10" t="n">
+        <f aca="false">px/E93</f>
+        <v>1.57395803232166</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="C98" s="10" t="n">
+        <f aca="false">IF(B98&gt;0,B98,"")</f>
+        <v>9.57</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="B99" s="14" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C99" s="10" t="n">
+        <f aca="false">IF(B99&gt;0,B99,"")</f>
+        <v>4.61</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C100" s="10" t="n">
+        <f aca="false">IF(B100&gt;0,B100,"")</f>
+        <v>2.54</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="B101" s="14" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C101" s="10" t="n">
+        <f aca="false">IF(B101&gt;0,B101,"")</f>
+        <v>30.2</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C102" s="10" t="n">
+        <f aca="false">IF(B102&gt;0,B102,"")</f>
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="C103" s="10" t="n">
+        <f aca="false">IF(B103&gt;0,B103,"")</f>
+        <v>9.01</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>9.38</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C104" s="10" t="n">
+        <f aca="false">IF(B104&gt;0,B104,"")</f>
+        <v>22.6</v>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>23.13</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="C105" s="10" t="str">
+        <f aca="false">IF(B105&gt;0,B105,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="C106" s="10" t="n">
+        <f aca="false">IF(B106&gt;0,B106,"")</f>
+        <v>5.99</v>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="B107" s="14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C107" s="10" t="n">
+        <f aca="false">IF(B107&gt;0,B107,"")</f>
+        <v>10.5</v>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="B108" s="10" t="n">
+        <f aca="false">PERCENTILE(B98:B107,0.25)</f>
+        <v>4.955</v>
+      </c>
+      <c r="C108" s="10" t="n">
+        <f aca="false">PERCENTILE(C98:C107,0.25)</f>
+        <v>5.99</v>
+      </c>
+      <c r="D108" s="10" t="n">
+        <f aca="false">PERCENTILE(D98:D107,0.25)</f>
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="B109" s="10" t="n">
+        <f aca="false">MEDIAN(B98:B107)</f>
+        <v>9.29</v>
+      </c>
+      <c r="C109" s="10" t="n">
+        <f aca="false">MEDIAN(C98:C107)</f>
+        <v>9.57</v>
+      </c>
+      <c r="D109" s="10" t="n">
+        <f aca="false">MEDIAN(D98:D107)</f>
+        <v>9.925</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="B110" s="10" t="n">
+        <f aca="false">PERCENTILE(B98:B107,0.75)</f>
+        <v>14.775</v>
+      </c>
+      <c r="C110" s="10" t="n">
+        <f aca="false">PERCENTILE(C98:C107,0.75)</f>
+        <v>16.2</v>
+      </c>
+      <c r="D110" s="10" t="n">
+        <f aca="false">PERCENTILE(D98:D107,0.75)</f>
+        <v>13.635</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B111" s="10" t="n">
+        <f aca="false">MIN(B98:B107)</f>
+        <v>-10.6</v>
+      </c>
+      <c r="C111" s="10" t="n">
+        <f aca="false">MIN(C98:C107)</f>
+        <v>2.54</v>
+      </c>
+      <c r="D111" s="10" t="n">
+        <f aca="false">MIN(D98:D107)</f>
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B112" s="10" t="n">
+        <f aca="false">MAX(B98:B107)</f>
+        <v>30.2</v>
+      </c>
+      <c r="C112" s="10" t="n">
+        <f aca="false">MAX(C98:C107)</f>
+        <v>30.2</v>
+      </c>
+      <c r="D112" s="10" t="n">
+        <f aca="false">MAX(D98:D107)</f>
+        <v>23.13</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B113" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(C108),2)</f>
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B114" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(C109),2)</f>
+        <v>9.57</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B115" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(C110),2)</f>
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B116" s="10" t="n">
+        <f aca="false">ROUND(MIN(C111),2)</f>
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="B117" s="10" t="n">
+        <f aca="false">ROUND(MAX(C112),2)</f>
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="C121" s="10" t="n">
+        <f aca="false">B113</f>
+        <v>5.99</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <f aca="false">Y!D29</f>
+        <v>550035.776345727</v>
+      </c>
+      <c r="F121" s="17" t="n">
+        <f aca="false">C121*E121</f>
+        <v>3294714.30031091</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <f aca="false">F121/px-1</f>
+        <v>0.912196343767211</v>
+      </c>
+      <c r="H121" s="10" t="n">
+        <f aca="false">px/E121</f>
+        <v>3.13252350864719</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="C122" s="10" t="n">
+        <f aca="false">B114</f>
+        <v>9.57</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <f aca="false">Y!D29</f>
+        <v>550035.776345727</v>
+      </c>
+      <c r="F122" s="17" t="n">
+        <f aca="false">C122*E122</f>
+        <v>5263842.37962861</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <f aca="false">F122/px-1</f>
+        <v>2.05504490982508</v>
+      </c>
+      <c r="H122" s="10" t="n">
+        <f aca="false">px/E122</f>
+        <v>3.13252350864719</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="C123" s="10" t="n">
+        <f aca="false">B115</f>
+        <v>16.2</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <f aca="false">Y!K29</f>
+        <v>195351.00901838</v>
+      </c>
+      <c r="F123" s="17" t="n">
+        <f aca="false">C123*E123</f>
+        <v>3164686.34609776</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <f aca="false">F123/px-1</f>
+        <v>0.836730322749717</v>
+      </c>
+      <c r="H123" s="10" t="n">
+        <f aca="false">px/E123</f>
+        <v>8.82002099020581</v>
       </c>
     </row>
   </sheetData>
@@ -35002,24 +37367,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>762</v>
+        <v>821</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>763</v>
+        <v>822</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>764</v>
+        <v>823</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>765</v>
+        <v>824</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>767</v>
+        <v>826</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35039,7 +37404,7 @@
         <v>712</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="C5" s="13" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -35059,7 +37424,7 @@
         <v>712</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -35079,7 +37444,7 @@
         <v>712</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>770</v>
+        <v>829</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -35099,7 +37464,7 @@
         <v>712</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -35119,7 +37484,7 @@
         <v>712</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -35139,7 +37504,7 @@
         <v>712</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -35171,7 +37536,7 @@
         <v>716</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -35191,7 +37556,7 @@
         <v>716</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -35211,7 +37576,7 @@
         <v>716</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>770</v>
+        <v>829</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -35231,7 +37596,7 @@
         <v>716</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -35251,7 +37616,7 @@
         <v>716</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -35271,7 +37636,7 @@
         <v>716</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -35303,7 +37668,7 @@
         <v>719</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -35323,7 +37688,7 @@
         <v>719</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -35343,7 +37708,7 @@
         <v>719</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>770</v>
+        <v>829</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -35363,7 +37728,7 @@
         <v>719</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -35383,7 +37748,7 @@
         <v>719</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -35403,7 +37768,7 @@
         <v>719</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -35435,7 +37800,7 @@
         <v>720</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="C29" s="13" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -35455,7 +37820,7 @@
         <v>720</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
       <c r="C30" s="13" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -35475,7 +37840,7 @@
         <v>720</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>770</v>
+        <v>829</v>
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -35495,7 +37860,7 @@
         <v>720</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="C32" s="13" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -35515,7 +37880,7 @@
         <v>720</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="C33" s="13" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -35535,7 +37900,7 @@
         <v>720</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="C34" s="13" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -35552,7 +37917,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>774</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -35580,7 +37945,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>775</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35588,21 +37953,21 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>776</v>
+        <v>835</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>777</v>
+        <v>836</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>778</v>
+        <v>837</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>779</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>780</v>
+        <v>839</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">Y!C4</f>
@@ -35616,12 +37981,12 @@
         <v>-0.00836946403295669</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>781</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>782</v>
+        <v>841</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">Y!C14</f>
@@ -35635,12 +38000,12 @@
         <v>-0.000839616405542865</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>783</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>784</v>
+        <v>843</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">Y!C20</f>
@@ -35654,12 +38019,12 @@
         <v>0.0337735275745357</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>785</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>786</v>
+        <v>845</v>
       </c>
       <c r="B7" s="13" t="n">
         <f aca="false">Y!C6</f>
@@ -35673,12 +38038,12 @@
         <v>-0.107661421776805</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>787</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">Y!D4</f>
@@ -35692,12 +38057,12 @@
         <v>0.000398596474166402</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>785</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>789</v>
+        <v>848</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">Y!D14</f>
@@ -35711,12 +38076,12 @@
         <v>0.0515932496365124</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>790</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>791</v>
+        <v>850</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">Y!D20</f>
@@ -35730,12 +38095,12 @@
         <v>0.0130416064099912</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>785</v>
+        <v>844</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>792</v>
+        <v>851</v>
       </c>
       <c r="B11" s="13" t="n">
         <f aca="false">Y!E14</f>
@@ -35749,12 +38114,12 @@
         <v>0.0571960438943868</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>793</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>794</v>
+        <v>853</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">Q!H4</f>
@@ -35768,12 +38133,12 @@
         <v>0.0234999470244424</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>795</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>796</v>
+        <v>855</v>
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">Q!H10</f>
@@ -35787,7 +38152,7 @@
         <v>-0.000178817722798708</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>797</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>
